--- a/data/trans_orig/P1433-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2012</t>
+          <t>Población con diagnóstico de esterilidad en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>697442</t>
+          <t>695772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>690255</t>
+          <t>689415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1391522</t>
+          <t>1391668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1399475</t>
+          <t>1399482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,97 +1074,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7435</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2145</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7467</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7515</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7818</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1015861</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1021506</t>
+          <t>1021538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2039103</t>
+          <t>2039406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>752541</t>
+          <t>752799</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>767632</t>
+          <t>767716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>775109</t>
+          <t>775114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1523647</t>
+          <t>1523567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1532650</t>
+          <t>1532633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>11350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>939761</t>
+          <t>940428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>946859</t>
+          <t>946848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1042419</t>
+          <t>1043171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1050033</t>
+          <t>1050038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1986664</t>
+          <t>1987327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1996732</t>
+          <t>1996810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3417071</t>
+          <t>3416382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3424980</t>
+          <t>3424960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3534381</t>
+          <t>3534272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3547939</t>
+          <t>3547779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6956174</t>
+          <t>6955798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6971552</t>
+          <t>6971068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2016</t>
+          <t>Población con diagnóstico de esterilidad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,97 +2678,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>672816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>674800</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670902</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>672839</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1345677</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1347639</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1015526</t>
+          <t>1015146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1037746</t>
+          <t>1038070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2057183</t>
+          <t>2057240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2064791</t>
+          <t>2064435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,96%</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,62 +3399,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5181</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>890</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4457</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>754377</t>
+          <t>755314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>782966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>785011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1540106</t>
+          <t>1539382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3707,97 +3707,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5132</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5197</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4944</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5384</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937567</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1038582</t>
+          <t>1038647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1975962</t>
+          <t>1976402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3386642</t>
+          <t>3386278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3393459</t>
+          <t>3393460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3538135</t>
+          <t>3537421</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6927755</t>
+          <t>6927469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6937064</t>
+          <t>6937054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">

--- a/data/trans_orig/P1433-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Habitat-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695772</t>
+          <t>696936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>689415</t>
+          <t>689357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1391668</t>
+          <t>1391672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1399482</t>
+          <t>1399476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1021538</t>
+          <t>1021435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2039406</t>
+          <t>2039399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>752799</t>
+          <t>752331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>767716</t>
+          <t>768351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>775114</t>
+          <t>775112</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1523567</t>
+          <t>1522572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1532633</t>
+          <t>1532648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>940428</t>
+          <t>940341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>946848</t>
+          <t>946854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1043171</t>
+          <t>1043264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1987327</t>
+          <t>1987488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1996810</t>
+          <t>1996791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3416382</t>
+          <t>3414510</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3424960</t>
+          <t>3424937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3534272</t>
+          <t>3534937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3547779</t>
+          <t>3548062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6955798</t>
+          <t>6956370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6971068</t>
+          <t>6970732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1015146</t>
+          <t>1015812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1038070</t>
+          <t>1037006</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2057240</t>
+          <t>2056392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2064435</t>
+          <t>2064430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>755314</t>
+          <t>755332</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1539382</t>
+          <t>1540104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1038647</t>
+          <t>1038664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1976402</t>
+          <t>1974548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3386278</t>
+          <t>3386768</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3393460</t>
+          <t>3393462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3537421</t>
+          <t>3537416</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6927469</t>
+          <t>6928632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6937054</t>
+          <t>6937069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
